--- a/capturas_guias_digemid/dig_ventas.xlsx
+++ b/capturas_guias_digemid/dig_ventas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:Q14"/>
   <cols>
     <col min="1" max="1" width="16.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -415,6 +415,7 @@
     <col min="14" max="14" width="14.83203125" customWidth="1"/>
     <col min="15" max="15" width="40.83203125" customWidth="1"/>
     <col min="16" max="16" width="40.83203125" customWidth="1"/>
+    <col min="17" max="17" width="24.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -536,6 +537,9 @@
       <c r="P4" t="str">
         <v>Punto de llegada</v>
       </c>
+      <c r="Q4" t="str">
+        <v>Guía sugerida (según nota, sin vincular)</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -548,31 +552,31 @@
         <v>F001</v>
       </c>
       <c r="D5" t="str">
-        <v>000006</v>
+        <v>000009</v>
       </c>
       <c r="E5" t="str">
-        <v>20111111111</v>
+        <v>20222222222</v>
       </c>
       <c r="F5" t="str">
-        <v>CLINICA UNO SAC</v>
+        <v>BOTICA DOS EIRL</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="K5" t="str">
         <v>PEN</v>
       </c>
       <c r="L5" t="str">
-        <v>Anulada</v>
+        <v>Emitida</v>
       </c>
       <c r="M5" t="str">
         <v/>
@@ -584,6 +588,9 @@
         <v/>
       </c>
       <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
         <v/>
       </c>
     </row>
@@ -598,7 +605,7 @@
         <v>F001</v>
       </c>
       <c r="D6" t="str">
-        <v>000005</v>
+        <v>000008</v>
       </c>
       <c r="E6" t="str">
         <v>20222222222</v>
@@ -634,6 +641,9 @@
         <v/>
       </c>
       <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
         <v/>
       </c>
     </row>
@@ -648,7 +658,7 @@
         <v>F001</v>
       </c>
       <c r="D7" t="str">
-        <v>000004</v>
+        <v>000007</v>
       </c>
       <c r="E7" t="str">
         <v>20222222222</v>
@@ -685,6 +695,9 @@
       </c>
       <c r="P7" t="str">
         <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v>TTT4-000010</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +711,31 @@
         <v>F001</v>
       </c>
       <c r="D8" t="str">
-        <v>000003</v>
+        <v>000006</v>
       </c>
       <c r="E8" t="str">
-        <v>20222222222</v>
+        <v>20111111111</v>
       </c>
       <c r="F8" t="str">
-        <v>BOTICA DOS EIRL</v>
+        <v>CLINICA UNO SAC</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="K8" t="str">
         <v>PEN</v>
       </c>
       <c r="L8" t="str">
-        <v>Emitida</v>
+        <v>Anulada</v>
       </c>
       <c r="M8" t="str">
         <v/>
@@ -734,6 +747,9 @@
         <v/>
       </c>
       <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
         <v/>
       </c>
     </row>
@@ -748,13 +764,13 @@
         <v>F001</v>
       </c>
       <c r="D9" t="str">
-        <v>000002</v>
+        <v>000005</v>
       </c>
       <c r="E9" t="str">
-        <v>20111111111</v>
+        <v>20222222222</v>
       </c>
       <c r="F9" t="str">
-        <v>CLINICA UNO SAC</v>
+        <v>BOTICA DOS EIRL</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -775,16 +791,19 @@
         <v>Emitida</v>
       </c>
       <c r="M9" t="str">
-        <v>TTT1-000002, TTT4-000001</v>
+        <v/>
       </c>
       <c r="N9" t="str">
-        <v>08/09/2026</v>
+        <v/>
       </c>
       <c r="O9" t="str">
-        <v>Partida de TTT1-000002 (150103) | Partida de TTT4-000001 (150103)</v>
+        <v/>
       </c>
       <c r="P9" t="str">
-        <v>Llegada de TTT1-000002 (150131) | Llegada de TTT4-000001 (150131)</v>
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -798,13 +817,13 @@
         <v>F001</v>
       </c>
       <c r="D10" t="str">
-        <v>000001</v>
+        <v>000004</v>
       </c>
       <c r="E10" t="str">
-        <v>20111111111</v>
+        <v>20222222222</v>
       </c>
       <c r="F10" t="str">
-        <v>CLINICA UNO SAC</v>
+        <v>BOTICA DOS EIRL</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -825,59 +844,221 @@
         <v>Emitida</v>
       </c>
       <c r="M10" t="str">
-        <v>TTT1-000001</v>
+        <v/>
       </c>
       <c r="N10" t="str">
-        <v>08/09/2026</v>
+        <v/>
       </c>
       <c r="O10" t="str">
-        <v>Partida de TTT1-000001 (150103)</v>
+        <v/>
       </c>
       <c r="P10" t="str">
-        <v>Llegada de TTT1-000001 (150131)</v>
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v/>
+        <v>2026-09-10</v>
       </c>
       <c r="B11" t="str">
-        <v/>
+        <v>FACTURA</v>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>F001</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>000003</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>20222222222</v>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>BOTICA DOS EIRL</v>
       </c>
       <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <v>18</v>
+      </c>
+      <c r="J11">
+        <v>118</v>
+      </c>
+      <c r="K11" t="str">
+        <v>PEN</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Emitida</v>
+      </c>
+      <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="B12" t="str">
+        <v>FACTURA</v>
+      </c>
+      <c r="C12" t="str">
+        <v>F001</v>
+      </c>
+      <c r="D12" t="str">
+        <v>000002</v>
+      </c>
+      <c r="E12" t="str">
+        <v>20111111111</v>
+      </c>
+      <c r="F12" t="str">
+        <v>CLINICA UNO SAC</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <v>18</v>
+      </c>
+      <c r="J12">
+        <v>118</v>
+      </c>
+      <c r="K12" t="str">
+        <v>PEN</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Emitida</v>
+      </c>
+      <c r="M12" t="str">
+        <v>TTT1-000002, TTT4-000001</v>
+      </c>
+      <c r="N12" t="str">
+        <v>08/09/2026</v>
+      </c>
+      <c r="O12" t="str">
+        <v>Partida de TTT1-000002 (150103) | Partida de TTT4-000001 (150103)</v>
+      </c>
+      <c r="P12" t="str">
+        <v>Llegada de TTT1-000002 (150131) | Llegada de TTT4-000001 (150131)</v>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2026-09-10</v>
+      </c>
+      <c r="B13" t="str">
+        <v>FACTURA</v>
+      </c>
+      <c r="C13" t="str">
+        <v>F001</v>
+      </c>
+      <c r="D13" t="str">
+        <v>000001</v>
+      </c>
+      <c r="E13" t="str">
+        <v>20111111111</v>
+      </c>
+      <c r="F13" t="str">
+        <v>CLINICA UNO SAC</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>118</v>
+      </c>
+      <c r="K13" t="str">
+        <v>PEN</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Emitida</v>
+      </c>
+      <c r="M13" t="str">
+        <v>TTT1-000001</v>
+      </c>
+      <c r="N13" t="str">
+        <v>08/09/2026</v>
+      </c>
+      <c r="O13" t="str">
+        <v>Partida de TTT1-000001 (150103)</v>
+      </c>
+      <c r="P13" t="str">
+        <v>Llegada de TTT1-000001 (150131)</v>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v/>
+      </c>
+      <c r="B14" t="str">
+        <v/>
+      </c>
+      <c r="C14" t="str">
+        <v/>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
         <v>Totales</v>
       </c>
-      <c r="H11">
-        <f>SUM(H5:H10)</f>
-      </c>
-      <c r="I11">
-        <f>SUM(I5:I10)</f>
-      </c>
-      <c r="J11">
-        <f>SUM(J5:J10)</f>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
+      <c r="H14">
+        <f>SUM(H5:H13)</f>
+      </c>
+      <c r="I14">
+        <f>SUM(I5:I13)</f>
+      </c>
+      <c r="J14">
+        <f>SUM(J5:J13)</f>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q14"/>
   </ignoredErrors>
 </worksheet>
 </file>